--- a/Шаблон Фурнитура.xlsx
+++ b/Шаблон Фурнитура.xlsx
@@ -998,7 +998,7 @@
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Конкретный цвет (Матовый никель/хром). Используется как отделка в карточке.</t>
+          <t>Отделка/цвет (Матовый никель/хром). Значение фильтра «Цвет» и отделка в карточке товара.</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>Группа цвета для фильтра «Цвет». Пусто — товар не попадёт в фильтр по цвету.</t>
+          <t>Для фурнитуры не используется, можно не заполнять.</t>
         </is>
       </c>
     </row>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Для фурнитуры в фильтрах не используется; можно не заполнять.</t>
+          <t>Для фурнитуры в фильтрах и карточке не используется; можно не заполнять.</t>
         </is>
       </c>
     </row>
